--- a/src/evaluation/data/Backup/qwen25_7b_validation/human_validation.xlsx
+++ b/src/evaluation/data/Backup/qwen25_7b_validation/human_validation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Köln\Masterarbeit\Software\uzk-masterarbeit\src\evaluation\data\Backup\qwen25_7b_validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10F2C24-7AFC-4DCA-8075-B75ADA492F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9E91EA-C3CB-43FC-9352-0A1E78D7F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ränge" sheetId="9" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -776,6 +776,21 @@
   </si>
   <si>
     <t>Anzahl 50-50</t>
+  </si>
+  <si>
+    <t>bert_f1</t>
+  </si>
+  <si>
+    <t>bert_precision</t>
+  </si>
+  <si>
+    <t>bert_recall</t>
+  </si>
+  <si>
+    <t>bert_f1 - semantic_similarity</t>
+  </si>
+  <si>
+    <t>F1 - answer_relevancy</t>
   </si>
 </sst>
 </file>
@@ -826,7 +841,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -881,6 +896,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -894,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -918,9 +939,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1223,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAAD467-ACD0-49ED-894B-B12CA7945213}">
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -1234,12 +1256,12 @@
     <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>157</v>
       </c>
@@ -1262,7 +1284,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1290,8 +1312,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O2,'Human Details'!$O$2:$O$16)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <f>_xlfn.RANK.EQ('Human Details'!M2,'Human Details'!$M$2:$M$16)</f>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <f>H3</f>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <f>I3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -1319,8 +1353,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O3,'Human Details'!$O$2:$O$16)</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <f>_xlfn.RANK.EQ('Human Details'!M3,'Human Details'!$M$2:$M$16)</f>
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:J17" si="0">H4</f>
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>11</v>
       </c>
@@ -1348,8 +1394,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O4,'Human Details'!$O$2:$O$16)</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <f>_xlfn.RANK.EQ('Human Details'!M4,'Human Details'!$M$2:$M$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>17</v>
       </c>
@@ -1377,8 +1435,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O5,'Human Details'!$O$2:$O$16)</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <f>_xlfn.RANK.EQ('Human Details'!M5,'Human Details'!$M$2:$M$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>20</v>
       </c>
@@ -1406,8 +1476,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O6,'Human Details'!$O$2:$O$16)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <f>_xlfn.RANK.EQ('Human Details'!M6,'Human Details'!$M$2:$M$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>30</v>
       </c>
@@ -1435,8 +1517,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O7,'Human Details'!$O$2:$O$16)</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <f>_xlfn.RANK.EQ('Human Details'!M7,'Human Details'!$M$2:$M$16)</f>
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>33</v>
       </c>
@@ -1464,8 +1558,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O8,'Human Details'!$O$2:$O$16)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f>_xlfn.RANK.EQ('Human Details'!M8,'Human Details'!$M$2:$M$16)</f>
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>34</v>
       </c>
@@ -1493,8 +1599,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O9,'Human Details'!$O$2:$O$16)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <f>_xlfn.RANK.EQ('Human Details'!M9,'Human Details'!$M$2:$M$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>64</v>
       </c>
@@ -1522,8 +1640,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O10,'Human Details'!$O$2:$O$16)</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <f>_xlfn.RANK.EQ('Human Details'!M10,'Human Details'!$M$2:$M$16)</f>
+        <v>13</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>65</v>
       </c>
@@ -1551,8 +1681,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O11,'Human Details'!$O$2:$O$16)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <f>_xlfn.RANK.EQ('Human Details'!M11,'Human Details'!$M$2:$M$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>84</v>
       </c>
@@ -1580,8 +1722,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O12,'Human Details'!$O$2:$O$16)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <f>_xlfn.RANK.EQ('Human Details'!M12,'Human Details'!$M$2:$M$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>89</v>
       </c>
@@ -1609,8 +1763,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O13,'Human Details'!$O$2:$O$16)</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <f>_xlfn.RANK.EQ('Human Details'!M13,'Human Details'!$M$2:$M$16)</f>
+        <v>13</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>91</v>
       </c>
@@ -1638,8 +1804,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O14,'Human Details'!$O$2:$O$16)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <f>_xlfn.RANK.EQ('Human Details'!M14,'Human Details'!$M$2:$M$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>97</v>
       </c>
@@ -1667,8 +1845,20 @@
         <f>_xlfn.RANK.EQ('Human Details'!O15,'Human Details'!$O$2:$O$16)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <f>_xlfn.RANK.EQ('Human Details'!M15,'Human Details'!$M$2:$M$16)</f>
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>110</v>
       </c>
@@ -1696,13 +1886,25 @@
         <f>_xlfn.RANK.EQ('Human Details'!O16,'Human Details'!$O$2:$O$16)</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <f>_xlfn.RANK.EQ('Human Details'!M16,'Human Details'!$M$2:$M$16)</f>
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>157</v>
       </c>
@@ -1725,7 +1927,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -1754,7 +1956,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>8</v>
       </c>
@@ -1783,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>11</v>
       </c>
@@ -1812,7 +2014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>17</v>
       </c>
@@ -1841,7 +2043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>20</v>
       </c>
@@ -1870,7 +2072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>30</v>
       </c>
@@ -1899,7 +2101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>33</v>
       </c>
@@ -1928,7 +2130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>34</v>
       </c>
@@ -1957,7 +2159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>64</v>
       </c>
@@ -1986,7 +2188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>65</v>
       </c>
@@ -2015,7 +2217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>84</v>
       </c>
@@ -4012,12 +4214,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>157</v>
       </c>
@@ -4039,8 +4241,17 @@
       <c r="G116" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" t="s">
+        <v>200</v>
+      </c>
+      <c r="I116" t="s">
+        <v>201</v>
+      </c>
+      <c r="J116" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1</v>
       </c>
@@ -4068,8 +4279,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O2,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U2,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>14</v>
+      </c>
+      <c r="I117">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V2,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>15</v>
+      </c>
+      <c r="J117">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W2,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>8</v>
       </c>
@@ -4097,8 +4320,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O3,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H118">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U3,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>15</v>
+      </c>
+      <c r="I118">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V3,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>14</v>
+      </c>
+      <c r="J118">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W3,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>11</v>
       </c>
@@ -4126,8 +4361,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O4,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H119">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U4,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>13</v>
+      </c>
+      <c r="I119">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V4,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>11</v>
+      </c>
+      <c r="J119">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W4,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>17</v>
       </c>
@@ -4155,8 +4402,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O5,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U5,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>4</v>
+      </c>
+      <c r="I120">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V5,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>4</v>
+      </c>
+      <c r="J120">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W5,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>20</v>
       </c>
@@ -4184,8 +4443,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O6,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U6,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>6</v>
+      </c>
+      <c r="I121">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V6,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>5</v>
+      </c>
+      <c r="J121">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W6,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>30</v>
       </c>
@@ -4213,8 +4484,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O7,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U7,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>2</v>
+      </c>
+      <c r="I122">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V7,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W7,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>33</v>
       </c>
@@ -4242,8 +4525,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O8,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U8,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V8,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>2</v>
+      </c>
+      <c r="J123">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W8,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>34</v>
       </c>
@@ -4271,8 +4566,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O9,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U9,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>11</v>
+      </c>
+      <c r="I124">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V9,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>12</v>
+      </c>
+      <c r="J124">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W9,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>64</v>
       </c>
@@ -4300,8 +4607,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O10,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H125">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U10,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>8</v>
+      </c>
+      <c r="I125">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V10,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>3</v>
+      </c>
+      <c r="J125">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W10,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>65</v>
       </c>
@@ -4329,8 +4648,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O11,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U11,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>12</v>
+      </c>
+      <c r="I126">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V11,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>6</v>
+      </c>
+      <c r="J126">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W11,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>84</v>
       </c>
@@ -4358,8 +4689,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O12,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H127">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U12,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>7</v>
+      </c>
+      <c r="I127">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V12,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>7</v>
+      </c>
+      <c r="J127">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W12,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>89</v>
       </c>
@@ -4387,8 +4730,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O13,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U13,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>9</v>
+      </c>
+      <c r="I128">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V13,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>10</v>
+      </c>
+      <c r="J128">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W13,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>91</v>
       </c>
@@ -4416,8 +4771,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O14,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U14,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>5</v>
+      </c>
+      <c r="I129">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V14,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>9</v>
+      </c>
+      <c r="J129">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W14,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>97</v>
       </c>
@@ -4445,8 +4812,20 @@
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O15,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U15,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>10</v>
+      </c>
+      <c r="I130">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V15,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>13</v>
+      </c>
+      <c r="J130">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W15,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>110</v>
       </c>
@@ -4473,6 +4852,18 @@
       <c r="G131">
         <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!O16,'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>8</v>
+      </c>
+      <c r="H131">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!U16,'gpt-4.1-mini-Details'!$U$2:$U$16)</f>
+        <v>3</v>
+      </c>
+      <c r="I131">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!V16,'gpt-4.1-mini-Details'!$V$2:$V$16)</f>
+        <v>8</v>
+      </c>
+      <c r="J131">
+        <f>_xlfn.RANK.EQ('gpt-4.1-mini-Details'!W16,'gpt-4.1-mini-Details'!$W$2:$W$16)</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6525,7 +6916,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D891E3DD-8A5C-4AA4-AD34-EFE870B9D592}">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="11" width="13" customWidth="1"/>
@@ -6536,9 +6927,12 @@
     <col min="16" max="17" width="10" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="15" customWidth="1"/>
+    <col min="23" max="23" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6599,8 +6993,17 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6661,8 +7064,17 @@
       <c r="T2">
         <v>31.847076416015621</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U2" s="3">
+        <v>0.83045172691345215</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.81123089790344238</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0.85060548782348633</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -6723,8 +7135,17 @@
       <c r="T3">
         <v>13.16566491127014</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U3" s="3">
+        <v>0.81646126508712769</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0.81617361307144165</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0.81674909591674805</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>11</v>
       </c>
@@ -6785,8 +7206,17 @@
       <c r="T4">
         <v>10.40932035446167</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U4" s="3">
+        <v>0.83335095643997192</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.83016705513000488</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.83655929565429688</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>17</v>
       </c>
@@ -6847,8 +7277,17 @@
       <c r="T5">
         <v>9.1491155624389648</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U5" s="3">
+        <v>0.86245894432067871</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0.85246396064758301</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0.87269103527069092</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>20</v>
       </c>
@@ -6909,8 +7348,17 @@
       <c r="T6">
         <v>18.27154541015625</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U6" s="3">
+        <v>0.84604948759078979</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0.85057801008224487</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0.84156882762908936</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>30</v>
       </c>
@@ -6971,8 +7419,17 @@
       <c r="T7">
         <v>11.04914927482605</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U7" s="3">
+        <v>0.88174992799758911</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0.87246608734130859</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0.89123344421386719</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>33</v>
       </c>
@@ -7033,8 +7490,17 @@
       <c r="T8">
         <v>9.1217787265777588</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U8" s="3">
+        <v>0.88948047161102295</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0.86122304201126099</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0.91965508460998535</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>34</v>
       </c>
@@ -7095,8 +7561,17 @@
       <c r="T9">
         <v>16.61525297164917</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U9" s="3">
+        <v>0.83638745546340942</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0.82234203815460205</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0.85092097520828247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>64</v>
       </c>
@@ -7157,8 +7632,17 @@
       <c r="T10">
         <v>11.4879937171936</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U10" s="3">
+        <v>0.84026753902435303</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0.85357481241226196</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0.82736885547637939</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>65</v>
       </c>
@@ -7219,8 +7703,17 @@
       <c r="T11">
         <v>24.864171504974369</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U11" s="3">
+        <v>0.8354496955871582</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0.84690839052200317</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0.82429707050323486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>84</v>
       </c>
@@ -7281,8 +7774,17 @@
       <c r="T12">
         <v>16.892225980758671</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U12" s="3">
+        <v>0.84338665008544922</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0.84652948379516602</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0.84026700258255005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>89</v>
       </c>
@@ -7343,8 +7845,17 @@
       <c r="T13">
         <v>18.279784679412838</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U13" s="3">
+        <v>0.8385690450668335</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.83162403106689453</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.84563100337982178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>91</v>
       </c>
@@ -7405,8 +7916,17 @@
       <c r="T14">
         <v>18.270648241043091</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U14" s="3">
+        <v>0.8525887131690979</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0.8406524658203125</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0.86486881971359253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>97</v>
       </c>
@@ -7467,8 +7987,17 @@
       <c r="T15">
         <v>25.263578414916989</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="U15" s="3">
+        <v>0.83766508102416992</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0.8213840126991272</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0.85460466146469116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>110</v>
       </c>
@@ -7528,6 +8057,15 @@
       </c>
       <c r="T16">
         <v>10.780250310897831</v>
+      </c>
+      <c r="U16" s="3">
+        <v>0.86877387762069702</v>
+      </c>
+      <c r="V16" s="3">
+        <v>0.84364545345306396</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0.89544516801834106</v>
       </c>
     </row>
   </sheetData>
@@ -9600,12 +10138,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -10152,13 +10690,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF1CBC7-6F83-4806-9A6E-B74BEDE7198D}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>186</v>
       </c>
@@ -10180,8 +10718,14 @@
       <c r="G1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>187</v>
       </c>
@@ -10210,7 +10754,7 @@
         <v>-0.14656358302837622</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>183</v>
       </c>
@@ -10239,7 +10783,7 @@
         <v>0.58980492603598622</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>184</v>
       </c>
@@ -10268,7 +10812,7 @@
         <v>0.20069750955391197</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>185</v>
       </c>
@@ -10297,7 +10841,7 @@
         <v>0.14822493412097942</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>189</v>
       </c>
@@ -10325,8 +10869,16 @@
         <f>CORREL(Ränge!G3:G17, Ränge!G117:G131)</f>
         <v>0.44812488093391351</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <f>CORREL(Ränge!H3:H17, Ränge!H117:H131)</f>
+        <v>6.4727273659829901E-2</v>
+      </c>
+      <c r="I6">
+        <f>CORREL(Ränge!G3:G17, Ränge!H117:H131)</f>
+        <v>-0.15594750091084561</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>188</v>
       </c>
@@ -10339,7 +10891,7 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="15" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
@@ -10349,7 +10901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>187</v>
       </c>
@@ -10365,7 +10917,7 @@
         <f>PEARSON('Human Details'!$L$2:$L$16, 'LLM-As-Judge Details'!$L$2:$L$16)</f>
         <v>0.41218722229223714</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="15">
         <f>PEARSON('Human Details'!$M$2:$M$16, 'LLM-As-Judge Details'!$M$2:$M$16)</f>
         <v>0.14385935125325996</v>
       </c>
@@ -10378,7 +10930,7 @@
         <v>0.37830877806043484</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>183</v>
       </c>
@@ -10394,7 +10946,7 @@
         <f>PEARSON('Human Details'!$L$2:$L$16, 'GPT4o-mini-Details'!$L$2:$L$16)</f>
         <v>0.58517311891033397</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="15">
         <f>PEARSON('Human Details'!$M$2:$M$16, 'GPT4o-mini-Details'!$M$2:$M$16)</f>
         <v>0.14385935125325996</v>
       </c>
@@ -10407,7 +10959,7 @@
         <v>0.69920986651411821</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>184</v>
       </c>
@@ -10423,7 +10975,7 @@
         <f>PEARSON('Human Details'!$L$2:$L$16, 'gpt-4.1-Details'!$L$2:$L$16)</f>
         <v>-0.1595596106936219</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="15">
         <f>PEARSON('Human Details'!$M$2:$M$16, 'gpt-4.1-Details'!$M$2:$M$16)</f>
         <v>-0.42476534468002053</v>
       </c>
@@ -10436,7 +10988,7 @@
         <v>0.31097902237946889</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>185</v>
       </c>
@@ -10452,7 +11004,7 @@
         <f>PEARSON('Human Details'!$L$2:$L$16, 'gpt-5.2-Details'!$L$2:$L$16)</f>
         <v>0.68822528049299581</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="15">
         <f>PEARSON('Human Details'!$M$2:$M$16, 'gpt-5.2-Details'!$M$2:$M$16)</f>
         <v>0.14385935125325996</v>
       </c>
@@ -10465,7 +11017,7 @@
         <v>0.40086275167273677</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>189</v>
       </c>
@@ -10481,7 +11033,7 @@
         <f>PEARSON('Human Details'!$L$2:$L$16, 'gpt-4.1-mini-Details'!$L$2:$L$16)</f>
         <v>0.55107579992168187</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="15">
         <f>PEARSON('Human Details'!$M$2:$M$16, 'gpt-4.1-mini-Details'!$M$2:$M$16)</f>
         <v>0.26938296177516874</v>
       </c>
@@ -10492,6 +11044,14 @@
       <c r="G14">
         <f>PEARSON('Human Details'!$O$2:$O$16, 'gpt-4.1-mini-Details'!$O$2:$O$16)</f>
         <v>0.46513087562715405</v>
+      </c>
+      <c r="H14">
+        <f>PEARSON('Human Details'!M2:M16, 'gpt-4.1-mini-Details'!U2:U16)</f>
+        <v>0.26636318073851917</v>
+      </c>
+      <c r="I14">
+        <f>PEARSON('Human Details'!O2:O16, 'gpt-4.1-mini-Details'!U2:U16)</f>
+        <v>-5.2512995839409063E-2</v>
       </c>
     </row>
   </sheetData>
@@ -12089,7 +12649,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB77051-8EA3-479A-8A81-74392105F5D0}">
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:AF87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
@@ -12263,7 +12823,7 @@
         <f>ABS('Human Details'!K3-'gpt-4.1-mini-Details'!K3)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4">
         <f>ABS('Human Details'!L3-'gpt-4.1-mini-Details'!L3)</f>
         <v>1</v>
       </c>
@@ -12290,7 +12850,7 @@
         <f>'gpt-4.1-mini-Details'!K3-'Human Details'!K3</f>
         <v>0</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4">
         <f>'gpt-4.1-mini-Details'!L3-'Human Details'!L3</f>
         <v>-1</v>
       </c>
@@ -12508,7 +13068,7 @@
         <f>ABS('Human Details'!J6-'gpt-4.1-mini-Details'!J6)</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7">
         <f>ABS('Human Details'!K6-'gpt-4.1-mini-Details'!K6)</f>
         <v>0.75</v>
       </c>
@@ -12535,7 +13095,7 @@
         <f>'gpt-4.1-mini-Details'!J6-'Human Details'!J6</f>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7">
         <f>'gpt-4.1-mini-Details'!K6-'Human Details'!K6</f>
         <v>-0.75</v>
       </c>
@@ -12591,11 +13151,11 @@
         <f>ABS('Human Details'!J7-'gpt-4.1-mini-Details'!J7)</f>
         <v>0.66666666666666674</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8">
         <f>ABS('Human Details'!K7-'gpt-4.1-mini-Details'!K7)</f>
         <v>1</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8">
         <f>ABS('Human Details'!L7-'gpt-4.1-mini-Details'!L7)</f>
         <v>0.75</v>
       </c>
@@ -12614,15 +13174,15 @@
       <c r="J8">
         <v>30</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8">
         <f>'gpt-4.1-mini-Details'!J7-'Human Details'!J7</f>
         <v>0.66666666666666674</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8">
         <f>'gpt-4.1-mini-Details'!K7-'Human Details'!K7</f>
         <v>1</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8">
         <f>'gpt-4.1-mini-Details'!L7-'Human Details'!L7</f>
         <v>-0.75</v>
       </c>
@@ -12935,7 +13495,7 @@
         <f>ABS('Human Details'!M11-'gpt-4.1-mini-Details'!M11)</f>
         <v>0.35285397946863595</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12">
         <f>ABS('Human Details'!N11-'gpt-4.1-mini-Details'!N11)</f>
         <v>0.87500000005208334</v>
       </c>
@@ -12954,7 +13514,7 @@
         <f>'gpt-4.1-mini-Details'!K11-'Human Details'!K11</f>
         <v>0</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12">
         <f>'gpt-4.1-mini-Details'!L11-'Human Details'!L11</f>
         <v>-0.66666666670000008</v>
       </c>
@@ -12962,7 +13522,7 @@
         <f>'gpt-4.1-mini-Details'!M11-'Human Details'!M11</f>
         <v>0.35285397946863595</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12">
         <f>'gpt-4.1-mini-Details'!N11-'Human Details'!N11</f>
         <v>-0.87500000005208334</v>
       </c>
@@ -13330,7 +13890,7 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>110</v>
       </c>
@@ -13338,7 +13898,7 @@
         <f>ABS('Human Details'!J16-'gpt-4.1-mini-Details'!J16)</f>
         <v>3.5714285714285698E-2</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17">
         <f>ABS('Human Details'!K16-'gpt-4.1-mini-Details'!K16)</f>
         <v>0.7</v>
       </c>
@@ -13365,7 +13925,7 @@
         <f>'gpt-4.1-mini-Details'!J16-'Human Details'!J16</f>
         <v>3.5714285714285698E-2</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17">
         <f>'gpt-4.1-mini-Details'!K16-'Human Details'!K16</f>
         <v>0.7</v>
       </c>
@@ -13413,7 +13973,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>9</v>
       </c>
@@ -13469,7 +14029,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -13477,7 +14037,7 @@
         <f>AVERAGE(B3:B17)</f>
         <v>0.18366621682411158</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20">
         <f t="shared" ref="C20:G20" si="0">AVERAGE(C3:C17)</f>
         <v>0.26047619047619042</v>
       </c>
@@ -13485,11 +14045,11 @@
         <f t="shared" si="0"/>
         <v>0.26611111112692593</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20">
         <f t="shared" si="0"/>
         <v>0.38264678044656164</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20">
         <f t="shared" si="0"/>
         <v>0.27638068562495172</v>
       </c>
@@ -13504,7 +14064,7 @@
         <f>AVERAGE(K3:K17)</f>
         <v>0.12144399460188933</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20">
         <f t="shared" ref="L20:P20" si="1">AVERAGE(L3:L17)</f>
         <v>0.11603174603174603</v>
       </c>
@@ -13512,11 +14072,11 @@
         <f t="shared" si="1"/>
         <v>-0.18092592595087656</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20">
         <f t="shared" si="1"/>
         <v>0.37487949327995179</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20">
         <f t="shared" si="1"/>
         <v>-4.0424634516792519E-2</v>
       </c>
@@ -13531,7 +14091,7 @@
         <f>AVERAGE(S3:S17)</f>
         <v>0.12840515693456872</v>
       </c>
-      <c r="T20" s="14">
+      <c r="T20">
         <f t="shared" ref="T20:X20" si="2">AVERAGE(T3:T17)</f>
         <v>0.18682539682539681</v>
       </c>
@@ -13539,11 +14099,11 @@
         <f t="shared" si="2"/>
         <v>-0.34275975166685957</v>
       </c>
-      <c r="V20" s="11">
+      <c r="V20">
         <f t="shared" si="2"/>
         <v>0.49655731675592774</v>
       </c>
-      <c r="W20" s="14">
+      <c r="W20">
         <f t="shared" si="2"/>
         <v>-0.6478692371845024</v>
       </c>
@@ -13552,16 +14112,10 @@
         <v>-0.15513886404384278</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" t="s">
-        <v>11</v>
-      </c>
       <c r="M23" t="s">
         <v>12</v>
       </c>
@@ -13571,8 +14125,14 @@
       <c r="U23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y23" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>157</v>
       </c>
@@ -13585,30 +14145,6 @@
       <c r="D24" t="s">
         <v>194</v>
       </c>
-      <c r="E24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F24" t="s">
-        <v>181</v>
-      </c>
-      <c r="G24" t="s">
-        <v>193</v>
-      </c>
-      <c r="H24" t="s">
-        <v>194</v>
-      </c>
-      <c r="I24" t="s">
-        <v>157</v>
-      </c>
-      <c r="J24" t="s">
-        <v>181</v>
-      </c>
-      <c r="K24" t="s">
-        <v>193</v>
-      </c>
-      <c r="L24" t="s">
-        <v>194</v>
-      </c>
       <c r="M24" t="s">
         <v>157</v>
       </c>
@@ -13645,12 +14181,36 @@
       <c r="X24" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y24" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>194</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>181</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="16">
         <f>'Human Details'!J2</f>
         <v>1</v>
       </c>
@@ -13661,38 +14221,10 @@
       <c r="D25" t="s">
         <v>195</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17">
-        <f>'Human Details'!K2</f>
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <f>'gpt-4.1-mini-Details'!K2</f>
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>195</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25" s="17">
-        <f>'Human Details'!L2</f>
-        <v>0.68</v>
-      </c>
-      <c r="K25">
-        <f>'gpt-4.1-mini-Details'!L2</f>
-        <v>0.47777777776185187</v>
-      </c>
-      <c r="L25" t="s">
-        <v>195</v>
-      </c>
       <c r="M25">
         <v>1</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="16">
         <f>'Human Details'!M2</f>
         <v>0.75</v>
       </c>
@@ -13706,7 +14238,7 @@
       <c r="Q25">
         <v>1</v>
       </c>
-      <c r="R25" s="17">
+      <c r="R25" s="16">
         <f>'Human Details'!N2</f>
         <v>0.45454545454545453</v>
       </c>
@@ -13717,7 +14249,7 @@
       <c r="U25">
         <v>1</v>
       </c>
-      <c r="V25" s="17">
+      <c r="V25" s="16">
         <f>'Human Details'!O2</f>
         <v>1</v>
       </c>
@@ -13728,12 +14260,40 @@
       <c r="X25" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="16">
+        <f>'Human Details'!M2</f>
+        <v>0.75</v>
+      </c>
+      <c r="AA25">
+        <f>'gpt-4.1-mini-Details'!U2</f>
+        <v>0.83045172691345215</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="16">
+        <f>'Human Details'!O2</f>
+        <v>1</v>
+      </c>
+      <c r="AE25">
+        <f>'gpt-4.1-mini-Details'!U2</f>
+        <v>0.83045172691345215</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>8</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <f>'Human Details'!J3</f>
         <v>0.5</v>
       </c>
@@ -13744,38 +14304,10 @@
       <c r="D26" t="s">
         <v>195</v>
       </c>
-      <c r="E26">
-        <v>8</v>
-      </c>
-      <c r="F26" s="17">
-        <f>'Human Details'!K3</f>
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <f>'gpt-4.1-mini-Details'!K3</f>
-        <v>0</v>
-      </c>
-      <c r="H26" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26" s="17">
-        <f>'Human Details'!L3</f>
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <f>'gpt-4.1-mini-Details'!L3</f>
-        <v>0</v>
-      </c>
-      <c r="L26" t="s">
-        <v>196</v>
-      </c>
       <c r="M26">
         <v>8</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="16">
         <f>'Human Details'!M3</f>
         <v>0</v>
       </c>
@@ -13789,7 +14321,7 @@
       <c r="Q26">
         <v>8</v>
       </c>
-      <c r="R26" s="17">
+      <c r="R26" s="16">
         <f>'Human Details'!N3</f>
         <v>0</v>
       </c>
@@ -13803,7 +14335,7 @@
       <c r="U26">
         <v>8</v>
       </c>
-      <c r="V26" s="17">
+      <c r="V26" s="16">
         <f>'Human Details'!O3</f>
         <v>0</v>
       </c>
@@ -13814,12 +14346,40 @@
       <c r="X26" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y26">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="16">
+        <f>'Human Details'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <f>'gpt-4.1-mini-Details'!U3</f>
+        <v>0.81646126508712769</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC26">
+        <v>8</v>
+      </c>
+      <c r="AD26" s="16">
+        <f>'Human Details'!O3</f>
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <f>'gpt-4.1-mini-Details'!U3</f>
+        <v>0.81646126508712769</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <f>'Human Details'!J4</f>
         <v>0.5</v>
       </c>
@@ -13827,38 +14387,10 @@
         <f>'gpt-4.1-mini-Details'!J4</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="E27">
-        <v>11</v>
-      </c>
-      <c r="F27" s="17">
-        <f>'Human Details'!K4</f>
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <f>'gpt-4.1-mini-Details'!K4</f>
-        <v>1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I27">
-        <v>11</v>
-      </c>
-      <c r="J27" s="17">
-        <f>'Human Details'!L4</f>
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <f>'gpt-4.1-mini-Details'!L4</f>
-        <v>0.99999999995</v>
-      </c>
-      <c r="L27" t="s">
-        <v>195</v>
-      </c>
       <c r="M27">
         <v>11</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="16">
         <f>'Human Details'!M4</f>
         <v>0.5</v>
       </c>
@@ -13872,7 +14404,7 @@
       <c r="Q27">
         <v>11</v>
       </c>
-      <c r="R27" s="17">
+      <c r="R27" s="16">
         <f>'Human Details'!N4</f>
         <v>0.27272727272727271</v>
       </c>
@@ -13886,7 +14418,7 @@
       <c r="U27">
         <v>11</v>
       </c>
-      <c r="V27" s="17">
+      <c r="V27" s="16">
         <f>'Human Details'!O4</f>
         <v>0.5</v>
       </c>
@@ -13897,12 +14429,37 @@
       <c r="X27" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y27">
+        <v>11</v>
+      </c>
+      <c r="Z27" s="16">
+        <f>'Human Details'!M4</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA27">
+        <f>'gpt-4.1-mini-Details'!U4</f>
+        <v>0.83335095643997192</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC27">
+        <v>11</v>
+      </c>
+      <c r="AD27" s="16">
+        <f>'Human Details'!O4</f>
+        <v>0.5</v>
+      </c>
+      <c r="AE27">
+        <f>'gpt-4.1-mini-Details'!U4</f>
+        <v>0.83335095643997192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>17</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <f>'Human Details'!J5</f>
         <v>0.66666666666666663</v>
       </c>
@@ -13913,38 +14470,10 @@
       <c r="D28" t="s">
         <v>195</v>
       </c>
-      <c r="E28">
-        <v>17</v>
-      </c>
-      <c r="F28" s="17">
-        <f>'Human Details'!K5</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G28">
-        <f>'gpt-4.1-mini-Details'!K5</f>
-        <v>0</v>
-      </c>
-      <c r="H28" t="s">
-        <v>195</v>
-      </c>
-      <c r="I28">
-        <v>17</v>
-      </c>
-      <c r="J28" s="17">
-        <f>'Human Details'!L5</f>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="K28">
-        <f>'gpt-4.1-mini-Details'!L5</f>
-        <v>0.19999999998000001</v>
-      </c>
-      <c r="L28" t="s">
-        <v>195</v>
-      </c>
       <c r="M28">
         <v>17</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="16">
         <f>'Human Details'!M5</f>
         <v>0.5</v>
       </c>
@@ -13958,7 +14487,7 @@
       <c r="Q28">
         <v>17</v>
       </c>
-      <c r="R28" s="17">
+      <c r="R28" s="16">
         <f>'Human Details'!N5</f>
         <v>0.33333333333333331</v>
       </c>
@@ -13972,7 +14501,7 @@
       <c r="U28">
         <v>17</v>
       </c>
-      <c r="V28" s="17">
+      <c r="V28" s="16">
         <f>'Human Details'!O5</f>
         <v>0.5</v>
       </c>
@@ -13980,12 +14509,37 @@
         <f>'gpt-4.1-mini-Details'!O5</f>
         <v>0.87199182957967969</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y28">
+        <v>17</v>
+      </c>
+      <c r="Z28" s="16">
+        <f>'Human Details'!M5</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA28">
+        <f>'gpt-4.1-mini-Details'!U5</f>
+        <v>0.86245894432067871</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC28">
+        <v>17</v>
+      </c>
+      <c r="AD28" s="16">
+        <f>'Human Details'!O5</f>
+        <v>0.5</v>
+      </c>
+      <c r="AE28">
+        <f>'gpt-4.1-mini-Details'!U5</f>
+        <v>0.86245894432067871</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>20</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <f>'Human Details'!J6</f>
         <v>0.9</v>
       </c>
@@ -13993,38 +14547,10 @@
         <f>'gpt-4.1-mini-Details'!J6</f>
         <v>0.6</v>
       </c>
-      <c r="E29">
-        <v>20</v>
-      </c>
-      <c r="F29" s="17">
-        <f>'Human Details'!K6</f>
-        <v>0.75</v>
-      </c>
-      <c r="G29">
-        <f>'gpt-4.1-mini-Details'!K6</f>
-        <v>0</v>
-      </c>
-      <c r="H29" t="s">
-        <v>196</v>
-      </c>
-      <c r="I29">
-        <v>20</v>
-      </c>
-      <c r="J29" s="17">
-        <f>'Human Details'!L6</f>
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <f>'gpt-4.1-mini-Details'!L6</f>
-        <v>0.99999999989999999</v>
-      </c>
-      <c r="L29" t="s">
-        <v>195</v>
-      </c>
       <c r="M29">
         <v>20</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="16">
         <f>'Human Details'!M6</f>
         <v>0.5</v>
       </c>
@@ -14038,7 +14564,7 @@
       <c r="Q29">
         <v>20</v>
       </c>
-      <c r="R29" s="17">
+      <c r="R29" s="16">
         <f>'Human Details'!N6</f>
         <v>0.25</v>
       </c>
@@ -14052,7 +14578,7 @@
       <c r="U29">
         <v>20</v>
       </c>
-      <c r="V29" s="17">
+      <c r="V29" s="16">
         <f>'Human Details'!O6</f>
         <v>0.8</v>
       </c>
@@ -14063,12 +14589,40 @@
       <c r="X29" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y29">
+        <v>20</v>
+      </c>
+      <c r="Z29" s="16">
+        <f>'Human Details'!M6</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA29">
+        <f>'gpt-4.1-mini-Details'!U6</f>
+        <v>0.84604948759078979</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC29">
+        <v>20</v>
+      </c>
+      <c r="AD29" s="16">
+        <f>'Human Details'!O6</f>
+        <v>0.8</v>
+      </c>
+      <c r="AE29">
+        <f>'gpt-4.1-mini-Details'!U6</f>
+        <v>0.84604948759078979</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>30</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <f>'Human Details'!J7</f>
         <v>0.33333333333333331</v>
       </c>
@@ -14079,38 +14633,10 @@
       <c r="D30" t="s">
         <v>196</v>
       </c>
-      <c r="E30">
-        <v>30</v>
-      </c>
-      <c r="F30" s="17">
-        <f>'Human Details'!K7</f>
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <f>'gpt-4.1-mini-Details'!K7</f>
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>196</v>
-      </c>
-      <c r="I30">
-        <v>30</v>
-      </c>
-      <c r="J30" s="17">
-        <f>'Human Details'!L7</f>
-        <v>0.75</v>
-      </c>
-      <c r="K30">
-        <f>'gpt-4.1-mini-Details'!L7</f>
-        <v>0</v>
-      </c>
-      <c r="L30" t="s">
-        <v>196</v>
-      </c>
       <c r="M30">
         <v>30</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="16">
         <f>'Human Details'!M7</f>
         <v>0.25</v>
       </c>
@@ -14124,7 +14650,7 @@
       <c r="Q30">
         <v>30</v>
       </c>
-      <c r="R30" s="17">
+      <c r="R30" s="16">
         <f>'Human Details'!N7</f>
         <v>0</v>
       </c>
@@ -14138,7 +14664,7 @@
       <c r="U30">
         <v>30</v>
       </c>
-      <c r="V30" s="17">
+      <c r="V30" s="16">
         <f>'Human Details'!O7</f>
         <v>0.25</v>
       </c>
@@ -14149,12 +14675,40 @@
       <c r="X30" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y30">
+        <v>30</v>
+      </c>
+      <c r="Z30" s="16">
+        <f>'Human Details'!M7</f>
+        <v>0.25</v>
+      </c>
+      <c r="AA30">
+        <f>'gpt-4.1-mini-Details'!U7</f>
+        <v>0.88174992799758911</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC30">
+        <v>30</v>
+      </c>
+      <c r="AD30" s="16">
+        <f>'Human Details'!O7</f>
+        <v>0.25</v>
+      </c>
+      <c r="AE30">
+        <f>'gpt-4.1-mini-Details'!U7</f>
+        <v>0.88174992799758911</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>33</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="16">
         <f>'Human Details'!J8</f>
         <v>0.5</v>
       </c>
@@ -14162,38 +14716,10 @@
         <f>'gpt-4.1-mini-Details'!J8</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="E31">
-        <v>33</v>
-      </c>
-      <c r="F31" s="17">
-        <f>'Human Details'!K8</f>
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <f>'gpt-4.1-mini-Details'!K8</f>
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>195</v>
-      </c>
-      <c r="I31">
-        <v>33</v>
-      </c>
-      <c r="J31" s="17">
-        <f>'Human Details'!L8</f>
-        <v>0.87</v>
-      </c>
-      <c r="K31">
-        <f>'gpt-4.1-mini-Details'!L8</f>
-        <v>0.8666666666377778</v>
-      </c>
-      <c r="L31" t="s">
-        <v>195</v>
-      </c>
       <c r="M31">
         <v>33</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N31" s="16">
         <f>'Human Details'!M8</f>
         <v>0.75</v>
       </c>
@@ -14207,7 +14733,7 @@
       <c r="Q31">
         <v>33</v>
       </c>
-      <c r="R31" s="17">
+      <c r="R31" s="16">
         <f>'Human Details'!N8</f>
         <v>1</v>
       </c>
@@ -14221,7 +14747,7 @@
       <c r="U31">
         <v>33</v>
       </c>
-      <c r="V31" s="17">
+      <c r="V31" s="16">
         <f>'Human Details'!O8</f>
         <v>0.75</v>
       </c>
@@ -14232,12 +14758,34 @@
       <c r="X31" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y31">
+        <v>33</v>
+      </c>
+      <c r="Z31" s="16">
+        <f>'Human Details'!M8</f>
+        <v>0.75</v>
+      </c>
+      <c r="AA31">
+        <f>'gpt-4.1-mini-Details'!U8</f>
+        <v>0.88948047161102295</v>
+      </c>
+      <c r="AC31">
+        <v>33</v>
+      </c>
+      <c r="AD31" s="16">
+        <f>'Human Details'!O8</f>
+        <v>0.75</v>
+      </c>
+      <c r="AE31">
+        <f>'gpt-4.1-mini-Details'!U8</f>
+        <v>0.88948047161102295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>34</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="16">
         <f>'Human Details'!J9</f>
         <v>0</v>
       </c>
@@ -14248,38 +14796,10 @@
       <c r="D32" t="s">
         <v>195</v>
       </c>
-      <c r="E32">
-        <v>34</v>
-      </c>
-      <c r="F32" s="17">
-        <f>'Human Details'!K9</f>
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <f>'gpt-4.1-mini-Details'!K9</f>
-        <v>0</v>
-      </c>
-      <c r="H32" t="s">
-        <v>195</v>
-      </c>
-      <c r="I32">
-        <v>34</v>
-      </c>
-      <c r="J32" s="17">
-        <f>'Human Details'!L9</f>
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <f>'gpt-4.1-mini-Details'!L9</f>
-        <v>0</v>
-      </c>
-      <c r="L32" t="s">
-        <v>195</v>
-      </c>
       <c r="M32">
         <v>34</v>
       </c>
-      <c r="N32" s="17">
+      <c r="N32" s="16">
         <f>'Human Details'!M9</f>
         <v>0.5</v>
       </c>
@@ -14293,7 +14813,7 @@
       <c r="Q32">
         <v>34</v>
       </c>
-      <c r="R32" s="17">
+      <c r="R32" s="16">
         <f>'Human Details'!N9</f>
         <v>0</v>
       </c>
@@ -14307,7 +14827,7 @@
       <c r="U32">
         <v>34</v>
       </c>
-      <c r="V32" s="17">
+      <c r="V32" s="16">
         <f>'Human Details'!O9</f>
         <v>1</v>
       </c>
@@ -14318,12 +14838,37 @@
       <c r="X32" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y32">
+        <v>34</v>
+      </c>
+      <c r="Z32" s="16">
+        <f>'Human Details'!M9</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA32">
+        <f>'gpt-4.1-mini-Details'!U9</f>
+        <v>0.83638745546340942</v>
+      </c>
+      <c r="AC32">
+        <v>34</v>
+      </c>
+      <c r="AD32" s="16">
+        <f>'Human Details'!O9</f>
+        <v>1</v>
+      </c>
+      <c r="AE32">
+        <f>'gpt-4.1-mini-Details'!U9</f>
+        <v>0.83638745546340942</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>64</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <f>'Human Details'!J10</f>
         <v>0</v>
       </c>
@@ -14334,38 +14879,10 @@
       <c r="D33" t="s">
         <v>195</v>
       </c>
-      <c r="E33">
-        <v>64</v>
-      </c>
-      <c r="F33" s="17">
-        <f>'Human Details'!K10</f>
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <f>'gpt-4.1-mini-Details'!K10</f>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="H33" t="s">
-        <v>195</v>
-      </c>
-      <c r="I33">
-        <v>64</v>
-      </c>
-      <c r="J33" s="17">
-        <f>'Human Details'!L10</f>
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <f>'gpt-4.1-mini-Details'!L10</f>
-        <v>0</v>
-      </c>
-      <c r="L33" t="s">
-        <v>195</v>
-      </c>
       <c r="M33">
         <v>64</v>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="16">
         <f>'Human Details'!M10</f>
         <v>0</v>
       </c>
@@ -14379,7 +14896,7 @@
       <c r="Q33">
         <v>64</v>
       </c>
-      <c r="R33" s="17">
+      <c r="R33" s="16">
         <f>'Human Details'!N10</f>
         <v>0</v>
       </c>
@@ -14393,7 +14910,7 @@
       <c r="U33">
         <v>64</v>
       </c>
-      <c r="V33" s="17">
+      <c r="V33" s="16">
         <f>'Human Details'!O10</f>
         <v>0</v>
       </c>
@@ -14404,12 +14921,40 @@
       <c r="X33" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y33">
+        <v>64</v>
+      </c>
+      <c r="Z33" s="16">
+        <f>'Human Details'!M10</f>
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <f>'gpt-4.1-mini-Details'!U10</f>
+        <v>0.84026753902435303</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC33">
+        <v>64</v>
+      </c>
+      <c r="AD33" s="16">
+        <f>'Human Details'!O10</f>
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <f>'gpt-4.1-mini-Details'!U10</f>
+        <v>0.84026753902435303</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>65</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <f>'Human Details'!J11</f>
         <v>0.66666666666666663</v>
       </c>
@@ -14420,38 +14965,10 @@
       <c r="D34" t="s">
         <v>195</v>
       </c>
-      <c r="E34">
-        <v>65</v>
-      </c>
-      <c r="F34" s="17">
-        <f>'Human Details'!K11</f>
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <f>'gpt-4.1-mini-Details'!K11</f>
-        <v>1</v>
-      </c>
-      <c r="H34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I34">
-        <v>65</v>
-      </c>
-      <c r="J34" s="17">
-        <f>'Human Details'!L11</f>
-        <v>1</v>
-      </c>
-      <c r="K34">
-        <f>'gpt-4.1-mini-Details'!L11</f>
-        <v>0.33333333329999998</v>
-      </c>
-      <c r="L34" t="s">
-        <v>196</v>
-      </c>
       <c r="M34">
         <v>65</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="16">
         <f>'Human Details'!M11</f>
         <v>0.5</v>
       </c>
@@ -14462,7 +14979,7 @@
       <c r="Q34">
         <v>65</v>
       </c>
-      <c r="R34" s="17">
+      <c r="R34" s="16">
         <f>'Human Details'!N11</f>
         <v>1</v>
       </c>
@@ -14476,7 +14993,7 @@
       <c r="U34">
         <v>65</v>
       </c>
-      <c r="V34" s="17">
+      <c r="V34" s="16">
         <f>'Human Details'!O11</f>
         <v>1</v>
       </c>
@@ -14487,12 +15004,37 @@
       <c r="X34" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y34">
+        <v>65</v>
+      </c>
+      <c r="Z34" s="16">
+        <f>'Human Details'!M11</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA34">
+        <f>'gpt-4.1-mini-Details'!U11</f>
+        <v>0.8354496955871582</v>
+      </c>
+      <c r="AC34">
+        <v>65</v>
+      </c>
+      <c r="AD34" s="16">
+        <f>'Human Details'!O11</f>
+        <v>1</v>
+      </c>
+      <c r="AE34">
+        <f>'gpt-4.1-mini-Details'!U11</f>
+        <v>0.8354496955871582</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>84</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="16">
         <f>'Human Details'!J12</f>
         <v>0.7142857142857143</v>
       </c>
@@ -14503,35 +15045,10 @@
       <c r="D35" t="s">
         <v>195</v>
       </c>
-      <c r="E35">
-        <v>84</v>
-      </c>
-      <c r="F35" s="17">
-        <f>'Human Details'!K12</f>
-        <v>0.4</v>
-      </c>
-      <c r="G35">
-        <f>'gpt-4.1-mini-Details'!K12</f>
-        <v>0.8</v>
-      </c>
-      <c r="I35">
-        <v>84</v>
-      </c>
-      <c r="J35" s="17">
-        <f>'Human Details'!L12</f>
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <f>'gpt-4.1-mini-Details'!L12</f>
-        <v>0.83333333329166659</v>
-      </c>
-      <c r="L35" t="s">
-        <v>195</v>
-      </c>
       <c r="M35">
         <v>84</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35" s="16">
         <f>'Human Details'!M12</f>
         <v>0.5</v>
       </c>
@@ -14545,7 +15062,7 @@
       <c r="Q35">
         <v>84</v>
       </c>
-      <c r="R35" s="17">
+      <c r="R35" s="16">
         <f>'Human Details'!N12</f>
         <v>0.11428571428571428</v>
       </c>
@@ -14559,7 +15076,7 @@
       <c r="U35">
         <v>84</v>
       </c>
-      <c r="V35" s="17">
+      <c r="V35" s="16">
         <f>'Human Details'!O12</f>
         <v>1</v>
       </c>
@@ -14570,12 +15087,37 @@
       <c r="X35" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y35">
+        <v>84</v>
+      </c>
+      <c r="Z35" s="16">
+        <f>'Human Details'!M12</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA35">
+        <f>'gpt-4.1-mini-Details'!U12</f>
+        <v>0.84338665008544922</v>
+      </c>
+      <c r="AC35">
+        <v>84</v>
+      </c>
+      <c r="AD35" s="16">
+        <f>'Human Details'!O12</f>
+        <v>1</v>
+      </c>
+      <c r="AE35">
+        <f>'gpt-4.1-mini-Details'!U12</f>
+        <v>0.84338665008544922</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>89</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="16">
         <f>'Human Details'!J13</f>
         <v>0</v>
       </c>
@@ -14586,38 +15128,10 @@
       <c r="D36" t="s">
         <v>195</v>
       </c>
-      <c r="E36">
-        <v>89</v>
-      </c>
-      <c r="F36" s="17">
-        <f>'Human Details'!K13</f>
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <f>'gpt-4.1-mini-Details'!K13</f>
-        <v>0</v>
-      </c>
-      <c r="H36" t="s">
-        <v>195</v>
-      </c>
-      <c r="I36">
-        <v>89</v>
-      </c>
-      <c r="J36" s="17">
-        <f>'Human Details'!L13</f>
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <f>'gpt-4.1-mini-Details'!L13</f>
-        <v>0</v>
-      </c>
-      <c r="L36" t="s">
-        <v>195</v>
-      </c>
       <c r="M36">
         <v>89</v>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="16">
         <f>'Human Details'!M13</f>
         <v>0</v>
       </c>
@@ -14631,7 +15145,7 @@
       <c r="Q36">
         <v>89</v>
       </c>
-      <c r="R36" s="17">
+      <c r="R36" s="16">
         <f>'Human Details'!N13</f>
         <v>0</v>
       </c>
@@ -14645,7 +15159,7 @@
       <c r="U36">
         <v>89</v>
       </c>
-      <c r="V36" s="17">
+      <c r="V36" s="16">
         <f>'Human Details'!O13</f>
         <v>0.2</v>
       </c>
@@ -14653,12 +15167,37 @@
         <f>'gpt-4.1-mini-Details'!O13</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y36">
+        <v>89</v>
+      </c>
+      <c r="Z36" s="16">
+        <f>'Human Details'!M13</f>
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <f>'gpt-4.1-mini-Details'!U13</f>
+        <v>0.8385690450668335</v>
+      </c>
+      <c r="AC36">
+        <v>89</v>
+      </c>
+      <c r="AD36" s="16">
+        <f>'Human Details'!O13</f>
+        <v>0.2</v>
+      </c>
+      <c r="AE36">
+        <f>'gpt-4.1-mini-Details'!U13</f>
+        <v>0.8385690450668335</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>91</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="16">
         <f>'Human Details'!J14</f>
         <v>0.46153846153846156</v>
       </c>
@@ -14669,35 +15208,10 @@
       <c r="D37" t="s">
         <v>195</v>
       </c>
-      <c r="E37">
-        <v>91</v>
-      </c>
-      <c r="F37" s="17">
-        <f>'Human Details'!K14</f>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="G37">
-        <f>'gpt-4.1-mini-Details'!K14</f>
-        <v>0.6</v>
-      </c>
-      <c r="H37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37">
-        <v>91</v>
-      </c>
-      <c r="J37" s="17">
-        <f>'Human Details'!L14</f>
-        <v>0.5</v>
-      </c>
-      <c r="K37">
-        <f>'gpt-4.1-mini-Details'!L14</f>
-        <v>0.83333333329166659</v>
-      </c>
       <c r="M37">
         <v>91</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N37" s="16">
         <f>'Human Details'!M14</f>
         <v>0.5</v>
       </c>
@@ -14708,7 +15222,7 @@
       <c r="Q37">
         <v>91</v>
       </c>
-      <c r="R37" s="17">
+      <c r="R37" s="16">
         <f>'Human Details'!N14</f>
         <v>0.65384615384615385</v>
       </c>
@@ -14719,7 +15233,7 @@
       <c r="U37">
         <v>91</v>
       </c>
-      <c r="V37" s="17">
+      <c r="V37" s="16">
         <f>'Human Details'!O14</f>
         <v>0.75</v>
       </c>
@@ -14730,12 +15244,34 @@
       <c r="X37" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y37">
+        <v>91</v>
+      </c>
+      <c r="Z37" s="16">
+        <f>'Human Details'!M14</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA37">
+        <f>'gpt-4.1-mini-Details'!U14</f>
+        <v>0.8525887131690979</v>
+      </c>
+      <c r="AC37">
+        <v>91</v>
+      </c>
+      <c r="AD37" s="16">
+        <f>'Human Details'!O14</f>
+        <v>0.75</v>
+      </c>
+      <c r="AE37">
+        <f>'gpt-4.1-mini-Details'!U14</f>
+        <v>0.8525887131690979</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>97</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="16">
         <f>'Human Details'!J15</f>
         <v>0.4</v>
       </c>
@@ -14746,35 +15282,10 @@
       <c r="D38" t="s">
         <v>196</v>
       </c>
-      <c r="E38">
-        <v>97</v>
-      </c>
-      <c r="F38" s="17">
-        <f>'Human Details'!K15</f>
-        <v>0.4</v>
-      </c>
-      <c r="G38">
-        <f>'gpt-4.1-mini-Details'!K15</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H38" t="s">
-        <v>195</v>
-      </c>
-      <c r="I38">
-        <v>97</v>
-      </c>
-      <c r="J38" s="17">
-        <f>'Human Details'!L15</f>
-        <v>0.5</v>
-      </c>
-      <c r="K38">
-        <f>'gpt-4.1-mini-Details'!L15</f>
-        <v>0.80555555552870362</v>
-      </c>
       <c r="M38">
         <v>97</v>
       </c>
-      <c r="N38" s="17">
+      <c r="N38" s="16">
         <f>'Human Details'!M15</f>
         <v>0.25</v>
       </c>
@@ -14788,7 +15299,7 @@
       <c r="Q38">
         <v>97</v>
       </c>
-      <c r="R38" s="17">
+      <c r="R38" s="16">
         <f>'Human Details'!N15</f>
         <v>0.6</v>
       </c>
@@ -14802,7 +15313,7 @@
       <c r="U38">
         <v>97</v>
       </c>
-      <c r="V38" s="17">
+      <c r="V38" s="16">
         <f>'Human Details'!O15</f>
         <v>0.75</v>
       </c>
@@ -14813,12 +15324,40 @@
       <c r="X38" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y38">
+        <v>97</v>
+      </c>
+      <c r="Z38" s="16">
+        <f>'Human Details'!M15</f>
+        <v>0.25</v>
+      </c>
+      <c r="AA38">
+        <f>'gpt-4.1-mini-Details'!U15</f>
+        <v>0.83766508102416992</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC38">
+        <v>97</v>
+      </c>
+      <c r="AD38" s="16">
+        <f>'Human Details'!O15</f>
+        <v>0.75</v>
+      </c>
+      <c r="AE38">
+        <f>'gpt-4.1-mini-Details'!U15</f>
+        <v>0.83766508102416992</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>110</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="16">
         <f>'Human Details'!J16</f>
         <v>0.25</v>
       </c>
@@ -14829,35 +15368,10 @@
       <c r="D39" t="s">
         <v>195</v>
       </c>
-      <c r="E39">
-        <v>110</v>
-      </c>
-      <c r="F39" s="17">
-        <f>'Human Details'!K16</f>
-        <v>0.3</v>
-      </c>
-      <c r="G39">
-        <f>'gpt-4.1-mini-Details'!K16</f>
-        <v>1</v>
-      </c>
-      <c r="H39" t="s">
-        <v>196</v>
-      </c>
-      <c r="I39">
-        <v>110</v>
-      </c>
-      <c r="J39" s="17">
-        <f>'Human Details'!L16</f>
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="K39">
-        <f>'gpt-4.1-mini-Details'!L16</f>
-        <v>0.47777777776185187</v>
-      </c>
       <c r="M39">
         <v>110</v>
       </c>
-      <c r="N39" s="17">
+      <c r="N39" s="16">
         <f>'Human Details'!M16</f>
         <v>0.25</v>
       </c>
@@ -14871,7 +15385,7 @@
       <c r="Q39">
         <v>110</v>
       </c>
-      <c r="R39" s="17">
+      <c r="R39" s="16">
         <f>'Human Details'!N16</f>
         <v>0.26315789473684209</v>
       </c>
@@ -14882,7 +15396,7 @@
       <c r="U39">
         <v>110</v>
       </c>
-      <c r="V39" s="17">
+      <c r="V39" s="16">
         <f>'Human Details'!O16</f>
         <v>0.25</v>
       </c>
@@ -14893,8 +15407,36 @@
       <c r="X39" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y39">
+        <v>110</v>
+      </c>
+      <c r="Z39" s="16">
+        <f>'Human Details'!M16</f>
+        <v>0.25</v>
+      </c>
+      <c r="AA39">
+        <f>'gpt-4.1-mini-Details'!U16</f>
+        <v>0.86877387762069702</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC39">
+        <v>110</v>
+      </c>
+      <c r="AD39" s="16">
+        <f>'Human Details'!O16</f>
+        <v>0.25</v>
+      </c>
+      <c r="AE39">
+        <f>'gpt-4.1-mini-Details'!U16</f>
+        <v>0.86877387762069702</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>197</v>
       </c>
@@ -14902,31 +15444,9 @@
         <f>COUNTIFS(D25:D39,"Ja")</f>
         <v>10</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41">
         <f>C41/15</f>
         <v>0.66666666666666663</v>
-      </c>
-      <c r="F41" t="s">
-        <v>197</v>
-      </c>
-      <c r="G41">
-        <f>COUNTIFS(H25:H39,"Ja")</f>
-        <v>11</v>
-      </c>
-      <c r="H41" s="13">
-        <f>G41/15</f>
-        <v>0.73333333333333328</v>
-      </c>
-      <c r="J41" t="s">
-        <v>197</v>
-      </c>
-      <c r="K41">
-        <f>COUNTIFS(L25:L39,"Ja")</f>
-        <v>9</v>
-      </c>
-      <c r="L41" s="13">
-        <f>K41/15</f>
-        <v>0.6</v>
       </c>
       <c r="N41" t="s">
         <v>197</v>
@@ -14935,7 +15455,7 @@
         <f>COUNTIFS(P25:P39,"Ja")</f>
         <v>7</v>
       </c>
-      <c r="P41" s="14">
+      <c r="P41">
         <f>O41/15</f>
         <v>0.46666666666666667</v>
       </c>
@@ -14946,7 +15466,7 @@
         <f>COUNTIFS(T25:T39,"Ja")</f>
         <v>8</v>
       </c>
-      <c r="T41" s="13">
+      <c r="T41">
         <f>S41/15</f>
         <v>0.53333333333333333</v>
       </c>
@@ -14961,8 +15481,30 @@
         <f>W41/15</f>
         <v>0.53333333333333333</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z41" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA41">
+        <f>COUNTIFS(AB25:AB39,"Ja")</f>
+        <v>6</v>
+      </c>
+      <c r="AB41">
+        <f>AA41/15</f>
+        <v>0.4</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE41">
+        <f>COUNTIFS(AF25:AF39,"Ja")</f>
+        <v>5</v>
+      </c>
+      <c r="AF41">
+        <f>AE41/15</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>198</v>
       </c>
@@ -14974,28 +15516,6 @@
         <f t="shared" ref="D42:D43" si="3">C42/15</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="F42" t="s">
-        <v>198</v>
-      </c>
-      <c r="G42">
-        <f>COUNTIFS(H25:H39,"Nein")</f>
-        <v>3</v>
-      </c>
-      <c r="H42">
-        <f t="shared" ref="H42:H43" si="4">G42/15</f>
-        <v>0.2</v>
-      </c>
-      <c r="J42" t="s">
-        <v>198</v>
-      </c>
-      <c r="K42">
-        <f>COUNTIFS(L25:L39,"Nein")</f>
-        <v>3</v>
-      </c>
-      <c r="L42">
-        <f t="shared" ref="L42:L43" si="5">K42/15</f>
-        <v>0.2</v>
-      </c>
       <c r="N42" t="s">
         <v>198</v>
       </c>
@@ -15003,8 +15523,8 @@
         <f>COUNTIFS(P25:P39,"Nein")</f>
         <v>6</v>
       </c>
-      <c r="P42" s="14">
-        <f t="shared" ref="P42:P43" si="6">O42/15</f>
+      <c r="P42">
+        <f t="shared" ref="P42:P43" si="4">O42/15</f>
         <v>0.4</v>
       </c>
       <c r="R42" t="s">
@@ -15015,7 +15535,7 @@
         <v>4</v>
       </c>
       <c r="T42">
-        <f t="shared" ref="T42:T43" si="7">S42/15</f>
+        <f t="shared" ref="T42:T43" si="5">S42/15</f>
         <v>0.26666666666666666</v>
       </c>
       <c r="V42" t="s">
@@ -15026,11 +15546,33 @@
         <v>5</v>
       </c>
       <c r="X42">
-        <f t="shared" ref="X42:X43" si="8">W42/15</f>
+        <f t="shared" ref="X42:X43" si="6">W42/15</f>
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z42" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA42">
+        <f>COUNTIFS(AB25:AB39,"Nein")</f>
+        <v>3</v>
+      </c>
+      <c r="AB42">
+        <f t="shared" ref="AB42:AB43" si="7">AA42/15</f>
+        <v>0.2</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>198</v>
+      </c>
+      <c r="AE42">
+        <f>COUNTIFS(AF25:AF39,"Nein")</f>
+        <v>6</v>
+      </c>
+      <c r="AF42">
+        <f t="shared" ref="AF42:AF43" si="8">AE42/15</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>199</v>
       </c>
@@ -15042,28 +15584,6 @@
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="F43" t="s">
-        <v>199</v>
-      </c>
-      <c r="G43">
-        <f>COUNTIFS(H25:H39,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <f t="shared" si="4"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="J43" t="s">
-        <v>199</v>
-      </c>
-      <c r="K43">
-        <f>COUNTIFS(L25:L39,"")</f>
-        <v>3</v>
-      </c>
-      <c r="L43">
-        <f t="shared" si="5"/>
-        <v>0.2</v>
-      </c>
       <c r="N43" t="s">
         <v>199</v>
       </c>
@@ -15072,7 +15592,7 @@
         <v>2</v>
       </c>
       <c r="P43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0.13333333333333333</v>
       </c>
       <c r="R43" t="s">
@@ -15083,7 +15603,7 @@
         <v>3</v>
       </c>
       <c r="T43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="V43" t="s">
@@ -15094,8 +15614,608 @@
         <v>2</v>
       </c>
       <c r="X43">
+        <f t="shared" si="6"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA43">
+        <f>COUNTIFS(AB25:AB39,"")</f>
+        <v>6</v>
+      </c>
+      <c r="AB43">
+        <f t="shared" si="7"/>
+        <v>0.4</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE43">
+        <f>COUNTIFS(AF25:AF39,"")</f>
+        <v>4</v>
+      </c>
+      <c r="AF43">
         <f t="shared" si="8"/>
-        <v>0.13333333333333333</v>
+        <v>0.26666666666666666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" t="s">
+        <v>181</v>
+      </c>
+      <c r="C46" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47" s="16">
+        <f>'Human Details'!K2</f>
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <f>'gpt-4.1-mini-Details'!K2</f>
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>8</v>
+      </c>
+      <c r="B48" s="16">
+        <f>'Human Details'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <f>'gpt-4.1-mini-Details'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>11</v>
+      </c>
+      <c r="B49" s="16">
+        <f>'Human Details'!K4</f>
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <f>'gpt-4.1-mini-Details'!K4</f>
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>17</v>
+      </c>
+      <c r="B50" s="16">
+        <f>'Human Details'!K5</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C50">
+        <f>'gpt-4.1-mini-Details'!K5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>20</v>
+      </c>
+      <c r="B51" s="16">
+        <f>'Human Details'!K6</f>
+        <v>0.75</v>
+      </c>
+      <c r="C51">
+        <f>'gpt-4.1-mini-Details'!K6</f>
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>30</v>
+      </c>
+      <c r="B52" s="16">
+        <f>'Human Details'!K7</f>
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <f>'gpt-4.1-mini-Details'!K7</f>
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>33</v>
+      </c>
+      <c r="B53" s="16">
+        <f>'Human Details'!K8</f>
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>'gpt-4.1-mini-Details'!K8</f>
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>34</v>
+      </c>
+      <c r="B54" s="16">
+        <f>'Human Details'!K9</f>
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <f>'gpt-4.1-mini-Details'!K9</f>
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>64</v>
+      </c>
+      <c r="B55" s="16">
+        <f>'Human Details'!K10</f>
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <f>'gpt-4.1-mini-Details'!K10</f>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>65</v>
+      </c>
+      <c r="B56" s="16">
+        <f>'Human Details'!K11</f>
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <f>'gpt-4.1-mini-Details'!K11</f>
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>84</v>
+      </c>
+      <c r="B57" s="16">
+        <f>'Human Details'!K12</f>
+        <v>0.4</v>
+      </c>
+      <c r="C57">
+        <f>'gpt-4.1-mini-Details'!K12</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>89</v>
+      </c>
+      <c r="B58" s="16">
+        <f>'Human Details'!K13</f>
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <f>'gpt-4.1-mini-Details'!K13</f>
+        <v>0</v>
+      </c>
+      <c r="D58" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>91</v>
+      </c>
+      <c r="B59" s="16">
+        <f>'Human Details'!K14</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="C59">
+        <f>'gpt-4.1-mini-Details'!K14</f>
+        <v>0.6</v>
+      </c>
+      <c r="D59" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>97</v>
+      </c>
+      <c r="B60" s="16">
+        <f>'Human Details'!K15</f>
+        <v>0.4</v>
+      </c>
+      <c r="C60">
+        <f>'gpt-4.1-mini-Details'!K15</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D60" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>110</v>
+      </c>
+      <c r="B61" s="16">
+        <f>'Human Details'!K16</f>
+        <v>0.3</v>
+      </c>
+      <c r="C61">
+        <f>'gpt-4.1-mini-Details'!K16</f>
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63">
+        <f>COUNTIFS(D47:D61,"Ja")</f>
+        <v>9</v>
+      </c>
+      <c r="D63">
+        <f>C63/15</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>198</v>
+      </c>
+      <c r="C64">
+        <f>COUNTIFS(D47:D61,"Nein")</f>
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <f t="shared" ref="D64:D65" si="9">C64/15</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>199</v>
+      </c>
+      <c r="C65">
+        <f>COUNTIFS(D47:D61,"")</f>
+        <v>3</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="9"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" t="s">
+        <v>181</v>
+      </c>
+      <c r="C68" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1</v>
+      </c>
+      <c r="B69" s="16">
+        <f>'Human Details'!L2</f>
+        <v>0.68</v>
+      </c>
+      <c r="C69">
+        <f>'gpt-4.1-mini-Details'!L2</f>
+        <v>0.47777777776185187</v>
+      </c>
+      <c r="D69" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>8</v>
+      </c>
+      <c r="B70" s="16">
+        <f>'Human Details'!L3</f>
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <f>'gpt-4.1-mini-Details'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="D70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>11</v>
+      </c>
+      <c r="B71" s="16">
+        <f>'Human Details'!L4</f>
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <f>'gpt-4.1-mini-Details'!L4</f>
+        <v>0.99999999995</v>
+      </c>
+      <c r="D71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>17</v>
+      </c>
+      <c r="B72" s="16">
+        <f>'Human Details'!L5</f>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="C72">
+        <f>'gpt-4.1-mini-Details'!L5</f>
+        <v>0.19999999998000001</v>
+      </c>
+      <c r="D72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>20</v>
+      </c>
+      <c r="B73" s="16">
+        <f>'Human Details'!L6</f>
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <f>'gpt-4.1-mini-Details'!L6</f>
+        <v>0.99999999989999999</v>
+      </c>
+      <c r="D73" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>30</v>
+      </c>
+      <c r="B74" s="16">
+        <f>'Human Details'!L7</f>
+        <v>0.75</v>
+      </c>
+      <c r="C74">
+        <f>'gpt-4.1-mini-Details'!L7</f>
+        <v>0</v>
+      </c>
+      <c r="D74" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>33</v>
+      </c>
+      <c r="B75" s="16">
+        <f>'Human Details'!L8</f>
+        <v>0.87</v>
+      </c>
+      <c r="C75">
+        <f>'gpt-4.1-mini-Details'!L8</f>
+        <v>0.8666666666377778</v>
+      </c>
+      <c r="D75" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>34</v>
+      </c>
+      <c r="B76" s="16">
+        <f>'Human Details'!L9</f>
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <f>'gpt-4.1-mini-Details'!L9</f>
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>64</v>
+      </c>
+      <c r="B77" s="16">
+        <f>'Human Details'!L10</f>
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <f>'gpt-4.1-mini-Details'!L10</f>
+        <v>0</v>
+      </c>
+      <c r="D77" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>65</v>
+      </c>
+      <c r="B78" s="16">
+        <f>'Human Details'!L11</f>
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <f>'gpt-4.1-mini-Details'!L11</f>
+        <v>0.33333333329999998</v>
+      </c>
+      <c r="D78" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>84</v>
+      </c>
+      <c r="B79" s="16">
+        <f>'Human Details'!L12</f>
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <f>'gpt-4.1-mini-Details'!L12</f>
+        <v>0.83333333329166659</v>
+      </c>
+      <c r="D79" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>89</v>
+      </c>
+      <c r="B80" s="16">
+        <f>'Human Details'!L13</f>
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <f>'gpt-4.1-mini-Details'!L13</f>
+        <v>0</v>
+      </c>
+      <c r="D80" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>91</v>
+      </c>
+      <c r="B81" s="16">
+        <f>'Human Details'!L14</f>
+        <v>0.5</v>
+      </c>
+      <c r="C81">
+        <f>'gpt-4.1-mini-Details'!L14</f>
+        <v>0.83333333329166659</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>97</v>
+      </c>
+      <c r="B82" s="16">
+        <f>'Human Details'!L15</f>
+        <v>0.5</v>
+      </c>
+      <c r="C82">
+        <f>'gpt-4.1-mini-Details'!L15</f>
+        <v>0.80555555552870362</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>110</v>
+      </c>
+      <c r="B83" s="16">
+        <f>'Human Details'!L16</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C83">
+        <f>'gpt-4.1-mini-Details'!L16</f>
+        <v>0.47777777776185187</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>197</v>
+      </c>
+      <c r="C85">
+        <f>COUNTIFS(D69:D83,"Ja")</f>
+        <v>9</v>
+      </c>
+      <c r="D85">
+        <f>C85/15</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>198</v>
+      </c>
+      <c r="C86">
+        <f>COUNTIFS(D69:D83,"Nein")</f>
+        <v>3</v>
+      </c>
+      <c r="D86">
+        <f t="shared" ref="D86:D87" si="10">C86/15</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>199</v>
+      </c>
+      <c r="C87">
+        <f>COUNTIFS(D69:D83,"")</f>
+        <v>3</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="10"/>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
